--- a/diseases/d221/2010-2014.xlsx
+++ b/diseases/d221/2010-2014.xlsx
@@ -1010,7 +1010,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3824,7 +3824,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4628,7 +4628,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5030,7 +5030,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5432,7 +5432,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5834,7 +5834,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6638,7 +6638,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7040,7 +7040,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7442,7 +7442,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7844,7 +7844,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8246,7 +8246,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8648,7 +8648,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -9050,7 +9050,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9452,7 +9452,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9854,7 +9854,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10658,7 +10658,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11060,7 +11060,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11462,7 +11462,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11864,7 +11864,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12266,7 +12266,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12668,7 +12668,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -13070,7 +13070,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13472,7 +13472,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14276,7 +14276,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14678,7 +14678,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -15080,7 +15080,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15482,7 +15482,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15884,7 +15884,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16286,7 +16286,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -17090,7 +17090,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17492,7 +17492,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17894,7 +17894,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18296,7 +18296,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18698,7 +18698,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -19100,7 +19100,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19502,7 +19502,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19904,7 +19904,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -20306,7 +20306,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20708,7 +20708,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -21110,7 +21110,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21512,7 +21512,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21914,7 +21914,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -22316,7 +22316,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -22718,7 +22718,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -23120,7 +23120,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23522,7 +23522,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23924,7 +23924,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -24326,7 +24326,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24728,7 +24728,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -25130,7 +25130,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25532,7 +25532,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -25934,7 +25934,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -26336,7 +26336,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -26738,7 +26738,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -27140,7 +27140,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -27542,7 +27542,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -27944,7 +27944,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -28346,7 +28346,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28748,7 +28748,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -29150,7 +29150,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -29552,7 +29552,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -29954,7 +29954,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -30356,7 +30356,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -30758,7 +30758,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -31160,7 +31160,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -31562,7 +31562,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -31964,7 +31964,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -32366,7 +32366,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -32768,7 +32768,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -33170,7 +33170,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -33572,7 +33572,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -33974,7 +33974,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -34376,7 +34376,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -34778,7 +34778,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -35180,7 +35180,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -35582,7 +35582,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -35984,7 +35984,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -36386,7 +36386,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -36788,7 +36788,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -37190,7 +37190,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -37592,7 +37592,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -37994,7 +37994,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -38396,7 +38396,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -38798,7 +38798,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -39200,7 +39200,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK193" t="inlineStr">
@@ -39602,7 +39602,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -40004,7 +40004,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK197" t="inlineStr">
@@ -40406,7 +40406,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -40808,7 +40808,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -41210,7 +41210,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -41612,7 +41612,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -42014,7 +42014,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -42416,7 +42416,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
@@ -42818,7 +42818,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -43220,7 +43220,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -43622,7 +43622,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -44024,7 +44024,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
@@ -44426,7 +44426,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -44828,7 +44828,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK221" t="inlineStr">
@@ -45230,7 +45230,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -45632,7 +45632,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -46034,7 +46034,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -46436,7 +46436,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -46838,7 +46838,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -47240,7 +47240,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -47642,7 +47642,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -48044,7 +48044,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -48446,7 +48446,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">
@@ -48848,7 +48848,7 @@
       </c>
       <c r="AJ241" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK241" t="inlineStr">

--- a/diseases/d221/2010-2014.xlsx
+++ b/diseases/d221/2010-2014.xlsx
@@ -1010,7 +1010,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3824,7 +3824,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4628,7 +4628,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5030,7 +5030,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5432,7 +5432,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5834,7 +5834,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6638,7 +6638,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7040,7 +7040,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7442,7 +7442,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7844,7 +7844,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8246,7 +8246,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8648,7 +8648,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -9050,7 +9050,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9452,7 +9452,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9854,7 +9854,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10658,7 +10658,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11060,7 +11060,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11462,7 +11462,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11864,7 +11864,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12266,7 +12266,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12668,7 +12668,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -13070,7 +13070,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13472,7 +13472,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14276,7 +14276,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14678,7 +14678,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -15080,7 +15080,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15482,7 +15482,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15884,7 +15884,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16286,7 +16286,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -17090,7 +17090,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17492,7 +17492,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17894,7 +17894,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18296,7 +18296,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18698,7 +18698,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -19100,7 +19100,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19502,7 +19502,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19904,7 +19904,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -20306,7 +20306,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20708,7 +20708,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -21110,7 +21110,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21512,7 +21512,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21914,7 +21914,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -22316,7 +22316,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -22718,7 +22718,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -23120,7 +23120,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23522,7 +23522,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23924,7 +23924,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -24326,7 +24326,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24728,7 +24728,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -25130,7 +25130,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25532,7 +25532,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -25934,7 +25934,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -26336,7 +26336,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -26738,7 +26738,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -27140,7 +27140,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -27542,7 +27542,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -27944,7 +27944,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -28346,7 +28346,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28748,7 +28748,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -29150,7 +29150,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -29552,7 +29552,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -29954,7 +29954,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -30356,7 +30356,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -30758,7 +30758,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -31160,7 +31160,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -31562,7 +31562,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -31964,7 +31964,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -32366,7 +32366,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -32768,7 +32768,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -33170,7 +33170,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -33572,7 +33572,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -33974,7 +33974,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -34376,7 +34376,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -34778,7 +34778,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -35180,7 +35180,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -35582,7 +35582,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -35984,7 +35984,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -36386,7 +36386,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -36788,7 +36788,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -37190,7 +37190,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -37592,7 +37592,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -37994,7 +37994,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -38396,7 +38396,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -38798,7 +38798,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -39200,7 +39200,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK193" t="inlineStr">
@@ -39602,7 +39602,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -40004,7 +40004,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK197" t="inlineStr">
@@ -40406,7 +40406,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -40808,7 +40808,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -41210,7 +41210,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -41612,7 +41612,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -42014,7 +42014,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -42416,7 +42416,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
@@ -42818,7 +42818,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -43220,7 +43220,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -43622,7 +43622,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -44024,7 +44024,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
@@ -44426,7 +44426,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -44828,7 +44828,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK221" t="inlineStr">
@@ -45230,7 +45230,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -45632,7 +45632,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -46034,7 +46034,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -46436,7 +46436,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -46838,7 +46838,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -47240,7 +47240,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -47642,7 +47642,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -48044,7 +48044,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -48446,7 +48446,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">
@@ -48848,7 +48848,7 @@
       </c>
       <c r="AJ241" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK241" t="inlineStr">

--- a/diseases/d221/2010-2014.xlsx
+++ b/diseases/d221/2010-2014.xlsx
@@ -1020,7 +1020,7 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN5" t="b">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -3834,7 +3834,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN17" t="b">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -4638,7 +4638,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -5040,7 +5040,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5442,7 +5442,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN25" t="b">
@@ -5844,7 +5844,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -6246,7 +6246,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -6648,7 +6648,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -7050,7 +7050,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -7452,7 +7452,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -8256,7 +8256,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -9060,7 +9060,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -9462,7 +9462,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -9864,7 +9864,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -10266,7 +10266,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -10668,7 +10668,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -11070,7 +11070,7 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN53" t="b">
@@ -11472,7 +11472,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -11874,7 +11874,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -12276,7 +12276,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -12678,7 +12678,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -13080,7 +13080,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -13482,7 +13482,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -13884,7 +13884,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -14286,7 +14286,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -14688,7 +14688,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -15090,7 +15090,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -15492,7 +15492,7 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN75" t="b">
@@ -15894,7 +15894,7 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN77" t="b">
@@ -16296,7 +16296,7 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN79" t="b">
@@ -16698,7 +16698,7 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -17100,7 +17100,7 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN83" t="b">
@@ -17502,7 +17502,7 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN85" t="b">
@@ -17904,7 +17904,7 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN87" t="b">
@@ -18306,7 +18306,7 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN89" t="b">
@@ -18708,7 +18708,7 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN91" t="b">
@@ -19110,7 +19110,7 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN93" t="b">
@@ -19512,7 +19512,7 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN95" t="b">
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN97" t="b">
@@ -20316,7 +20316,7 @@
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN99" t="b">
@@ -20718,7 +20718,7 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN101" t="b">
@@ -21120,7 +21120,7 @@
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN103" t="b">
@@ -21522,7 +21522,7 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN105" t="b">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN107" t="b">
@@ -22326,7 +22326,7 @@
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN109" t="b">
@@ -22728,7 +22728,7 @@
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN111" t="b">
@@ -23130,7 +23130,7 @@
       </c>
       <c r="AM113" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN113" t="b">
@@ -23532,7 +23532,7 @@
       </c>
       <c r="AM115" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN115" t="b">
@@ -23934,7 +23934,7 @@
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN117" t="b">
@@ -24336,7 +24336,7 @@
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN119" t="b">
@@ -24738,7 +24738,7 @@
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN121" t="b">
@@ -25140,7 +25140,7 @@
       </c>
       <c r="AM123" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN123" t="b">
@@ -25542,7 +25542,7 @@
       </c>
       <c r="AM125" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN125" t="b">
@@ -25944,7 +25944,7 @@
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN127" t="b">
@@ -26346,7 +26346,7 @@
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN129" t="b">
@@ -26748,7 +26748,7 @@
       </c>
       <c r="AM131" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN131" t="b">
@@ -27150,7 +27150,7 @@
       </c>
       <c r="AM133" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN133" t="b">
@@ -27552,7 +27552,7 @@
       </c>
       <c r="AM135" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN135" t="b">
@@ -27954,7 +27954,7 @@
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN137" t="b">
@@ -28356,7 +28356,7 @@
       </c>
       <c r="AM139" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN139" t="b">
@@ -28758,7 +28758,7 @@
       </c>
       <c r="AM141" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN141" t="b">
@@ -29160,7 +29160,7 @@
       </c>
       <c r="AM143" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN143" t="b">
@@ -29562,7 +29562,7 @@
       </c>
       <c r="AM145" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN145" t="b">
@@ -29964,7 +29964,7 @@
       </c>
       <c r="AM147" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN147" t="b">
@@ -30366,7 +30366,7 @@
       </c>
       <c r="AM149" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN149" t="b">
@@ -30768,7 +30768,7 @@
       </c>
       <c r="AM151" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN151" t="b">
@@ -31170,7 +31170,7 @@
       </c>
       <c r="AM153" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN153" t="b">
@@ -31572,7 +31572,7 @@
       </c>
       <c r="AM155" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN155" t="b">
@@ -31974,7 +31974,7 @@
       </c>
       <c r="AM157" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN157" t="b">
@@ -32376,7 +32376,7 @@
       </c>
       <c r="AM159" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN159" t="b">
@@ -32778,7 +32778,7 @@
       </c>
       <c r="AM161" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN161" t="b">
@@ -33180,7 +33180,7 @@
       </c>
       <c r="AM163" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN163" t="b">
@@ -33582,7 +33582,7 @@
       </c>
       <c r="AM165" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN165" t="b">
@@ -33984,7 +33984,7 @@
       </c>
       <c r="AM167" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN167" t="b">
@@ -34386,7 +34386,7 @@
       </c>
       <c r="AM169" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN169" t="b">
@@ -34788,7 +34788,7 @@
       </c>
       <c r="AM171" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN171" t="b">
@@ -35190,7 +35190,7 @@
       </c>
       <c r="AM173" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN173" t="b">
@@ -35592,7 +35592,7 @@
       </c>
       <c r="AM175" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN175" t="b">
@@ -35994,7 +35994,7 @@
       </c>
       <c r="AM177" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN177" t="b">
@@ -36396,7 +36396,7 @@
       </c>
       <c r="AM179" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN179" t="b">
@@ -36798,7 +36798,7 @@
       </c>
       <c r="AM181" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN181" t="b">
@@ -37200,7 +37200,7 @@
       </c>
       <c r="AM183" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN183" t="b">
@@ -37602,7 +37602,7 @@
       </c>
       <c r="AM185" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN185" t="b">
@@ -38004,7 +38004,7 @@
       </c>
       <c r="AM187" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN187" t="b">
@@ -38406,7 +38406,7 @@
       </c>
       <c r="AM189" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN189" t="b">
@@ -38808,7 +38808,7 @@
       </c>
       <c r="AM191" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN191" t="b">
@@ -39210,7 +39210,7 @@
       </c>
       <c r="AM193" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN193" t="b">
@@ -39612,7 +39612,7 @@
       </c>
       <c r="AM195" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN195" t="b">
@@ -40014,7 +40014,7 @@
       </c>
       <c r="AM197" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN197" t="b">
@@ -40416,7 +40416,7 @@
       </c>
       <c r="AM199" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN199" t="b">
@@ -40818,7 +40818,7 @@
       </c>
       <c r="AM201" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN201" t="b">
@@ -41220,7 +41220,7 @@
       </c>
       <c r="AM203" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN203" t="b">
@@ -41622,7 +41622,7 @@
       </c>
       <c r="AM205" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN205" t="b">
@@ -42024,7 +42024,7 @@
       </c>
       <c r="AM207" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN207" t="b">
@@ -42426,7 +42426,7 @@
       </c>
       <c r="AM209" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN209" t="b">
@@ -42828,7 +42828,7 @@
       </c>
       <c r="AM211" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN211" t="b">
@@ -43230,7 +43230,7 @@
       </c>
       <c r="AM213" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN213" t="b">
@@ -43632,7 +43632,7 @@
       </c>
       <c r="AM215" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN215" t="b">
@@ -44034,7 +44034,7 @@
       </c>
       <c r="AM217" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN217" t="b">
@@ -44436,7 +44436,7 @@
       </c>
       <c r="AM219" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN219" t="b">
@@ -44838,7 +44838,7 @@
       </c>
       <c r="AM221" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN221" t="b">
@@ -45240,7 +45240,7 @@
       </c>
       <c r="AM223" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN223" t="b">
@@ -45642,7 +45642,7 @@
       </c>
       <c r="AM225" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN225" t="b">
@@ -46044,7 +46044,7 @@
       </c>
       <c r="AM227" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN227" t="b">
@@ -46446,7 +46446,7 @@
       </c>
       <c r="AM229" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN229" t="b">
@@ -46848,7 +46848,7 @@
       </c>
       <c r="AM231" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN231" t="b">
@@ -47250,7 +47250,7 @@
       </c>
       <c r="AM233" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN233" t="b">
@@ -47652,7 +47652,7 @@
       </c>
       <c r="AM235" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN235" t="b">
@@ -48054,7 +48054,7 @@
       </c>
       <c r="AM237" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN237" t="b">
@@ -48456,7 +48456,7 @@
       </c>
       <c r="AM239" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN239" t="b">
@@ -48858,7 +48858,7 @@
       </c>
       <c r="AM241" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN241" t="b">

--- a/diseases/d221/2010-2014.xlsx
+++ b/diseases/d221/2010-2014.xlsx
@@ -1010,7 +1010,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3824,7 +3824,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4628,7 +4628,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5030,7 +5030,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5432,7 +5432,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5834,7 +5834,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6638,7 +6638,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7040,7 +7040,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7442,7 +7442,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7844,7 +7844,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8246,7 +8246,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8648,7 +8648,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -9050,7 +9050,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9452,7 +9452,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9854,7 +9854,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10658,7 +10658,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11060,7 +11060,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11462,7 +11462,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11864,7 +11864,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12266,7 +12266,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12668,7 +12668,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -13070,7 +13070,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13472,7 +13472,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14276,7 +14276,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14678,7 +14678,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -15080,7 +15080,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15482,7 +15482,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15884,7 +15884,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16286,7 +16286,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -17090,7 +17090,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17492,7 +17492,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17894,7 +17894,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18296,7 +18296,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18698,7 +18698,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -19100,7 +19100,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19502,7 +19502,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19904,7 +19904,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -20306,7 +20306,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20708,7 +20708,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -21110,7 +21110,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21512,7 +21512,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21914,7 +21914,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -22316,7 +22316,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -22718,7 +22718,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -23120,7 +23120,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23522,7 +23522,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23924,7 +23924,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -24326,7 +24326,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24728,7 +24728,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -25130,7 +25130,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25532,7 +25532,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -25934,7 +25934,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -26336,7 +26336,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -26738,7 +26738,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -27140,7 +27140,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -27542,7 +27542,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -27944,7 +27944,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -28346,7 +28346,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28748,7 +28748,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -29150,7 +29150,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -29552,7 +29552,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -29954,7 +29954,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -30356,7 +30356,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -30758,7 +30758,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -31160,7 +31160,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -31562,7 +31562,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -31964,7 +31964,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -32366,7 +32366,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -32768,7 +32768,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -33170,7 +33170,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -33572,7 +33572,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -33974,7 +33974,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -34376,7 +34376,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -34778,7 +34778,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -35180,7 +35180,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -35582,7 +35582,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -35984,7 +35984,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -36386,7 +36386,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -36788,7 +36788,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -37190,7 +37190,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -37592,7 +37592,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -37994,7 +37994,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -38396,7 +38396,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -38798,7 +38798,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -39200,7 +39200,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK193" t="inlineStr">
@@ -39602,7 +39602,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -40004,7 +40004,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK197" t="inlineStr">
@@ -40406,7 +40406,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -40808,7 +40808,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -41210,7 +41210,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -41612,7 +41612,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -42014,7 +42014,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -42416,7 +42416,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
@@ -42818,7 +42818,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -43220,7 +43220,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -43622,7 +43622,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -44024,7 +44024,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
@@ -44426,7 +44426,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -44828,7 +44828,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK221" t="inlineStr">
@@ -45230,7 +45230,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -45632,7 +45632,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -46034,7 +46034,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -46436,7 +46436,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -46838,7 +46838,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -47240,7 +47240,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -47642,7 +47642,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -48044,7 +48044,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -48446,7 +48446,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">
@@ -48848,7 +48848,7 @@
       </c>
       <c r="AJ241" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK241" t="inlineStr">

--- a/diseases/d221/2010-2014.xlsx
+++ b/diseases/d221/2010-2014.xlsx
@@ -1010,7 +1010,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3824,7 +3824,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4628,7 +4628,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5030,7 +5030,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5432,7 +5432,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5834,7 +5834,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6638,7 +6638,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7040,7 +7040,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7442,7 +7442,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7844,7 +7844,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8246,7 +8246,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8648,7 +8648,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -9050,7 +9050,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9452,7 +9452,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9854,7 +9854,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10658,7 +10658,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11060,7 +11060,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11462,7 +11462,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11864,7 +11864,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12266,7 +12266,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12668,7 +12668,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -13070,7 +13070,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13472,7 +13472,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14276,7 +14276,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14678,7 +14678,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -15080,7 +15080,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15482,7 +15482,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15884,7 +15884,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16286,7 +16286,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -17090,7 +17090,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17492,7 +17492,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17894,7 +17894,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18296,7 +18296,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18698,7 +18698,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -19100,7 +19100,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19502,7 +19502,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19904,7 +19904,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -20306,7 +20306,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20708,7 +20708,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -21110,7 +21110,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21512,7 +21512,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21914,7 +21914,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -22316,7 +22316,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -22718,7 +22718,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -23120,7 +23120,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23522,7 +23522,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23924,7 +23924,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -24326,7 +24326,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24728,7 +24728,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -25130,7 +25130,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25532,7 +25532,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -25934,7 +25934,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -26336,7 +26336,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -26738,7 +26738,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -27140,7 +27140,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -27542,7 +27542,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -27944,7 +27944,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -28346,7 +28346,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28748,7 +28748,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -29150,7 +29150,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -29552,7 +29552,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -29954,7 +29954,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -30356,7 +30356,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -30758,7 +30758,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -31160,7 +31160,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -31562,7 +31562,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -31964,7 +31964,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -32366,7 +32366,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -32768,7 +32768,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -33170,7 +33170,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -33572,7 +33572,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -33974,7 +33974,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -34376,7 +34376,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -34778,7 +34778,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -35180,7 +35180,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -35582,7 +35582,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -35984,7 +35984,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -36386,7 +36386,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -36788,7 +36788,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -37190,7 +37190,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -37592,7 +37592,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -37994,7 +37994,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -38396,7 +38396,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -38798,7 +38798,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -39200,7 +39200,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK193" t="inlineStr">
@@ -39602,7 +39602,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -40004,7 +40004,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK197" t="inlineStr">
@@ -40406,7 +40406,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -40808,7 +40808,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -41210,7 +41210,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -41612,7 +41612,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -42014,7 +42014,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -42416,7 +42416,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
@@ -42818,7 +42818,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -43220,7 +43220,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -43622,7 +43622,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -44024,7 +44024,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
@@ -44426,7 +44426,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -44828,7 +44828,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK221" t="inlineStr">
@@ -45230,7 +45230,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -45632,7 +45632,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -46034,7 +46034,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -46436,7 +46436,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -46838,7 +46838,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -47240,7 +47240,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -47642,7 +47642,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -48044,7 +48044,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -48446,7 +48446,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">
@@ -48848,7 +48848,7 @@
       </c>
       <c r="AJ241" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK241" t="inlineStr">

--- a/diseases/d221/2010-2014.xlsx
+++ b/diseases/d221/2010-2014.xlsx
@@ -1010,7 +1010,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3824,7 +3824,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4628,7 +4628,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5030,7 +5030,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5432,7 +5432,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5834,7 +5834,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6638,7 +6638,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7040,7 +7040,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7442,7 +7442,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7844,7 +7844,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8246,7 +8246,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8648,7 +8648,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -9050,7 +9050,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9452,7 +9452,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9854,7 +9854,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10658,7 +10658,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11060,7 +11060,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11462,7 +11462,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11864,7 +11864,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12266,7 +12266,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12668,7 +12668,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -13070,7 +13070,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13472,7 +13472,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14276,7 +14276,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14678,7 +14678,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -15080,7 +15080,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15482,7 +15482,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15884,7 +15884,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16286,7 +16286,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -17090,7 +17090,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17492,7 +17492,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17894,7 +17894,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18296,7 +18296,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18698,7 +18698,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -19100,7 +19100,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19502,7 +19502,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19904,7 +19904,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -20306,7 +20306,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20708,7 +20708,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -21110,7 +21110,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21512,7 +21512,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21914,7 +21914,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -22316,7 +22316,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -22718,7 +22718,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -23120,7 +23120,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23522,7 +23522,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23924,7 +23924,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -24326,7 +24326,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24728,7 +24728,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -25130,7 +25130,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25532,7 +25532,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -25934,7 +25934,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -26336,7 +26336,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -26738,7 +26738,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -27140,7 +27140,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -27542,7 +27542,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -27944,7 +27944,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -28346,7 +28346,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28748,7 +28748,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -29150,7 +29150,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -29552,7 +29552,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -29954,7 +29954,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -30356,7 +30356,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -30758,7 +30758,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -31160,7 +31160,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -31562,7 +31562,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -31964,7 +31964,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -32366,7 +32366,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -32768,7 +32768,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -33170,7 +33170,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -33572,7 +33572,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -33974,7 +33974,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -34376,7 +34376,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -34778,7 +34778,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -35180,7 +35180,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -35582,7 +35582,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -35984,7 +35984,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -36386,7 +36386,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -36788,7 +36788,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -37190,7 +37190,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -37592,7 +37592,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -37994,7 +37994,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -38396,7 +38396,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -38798,7 +38798,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -39200,7 +39200,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK193" t="inlineStr">
@@ -39602,7 +39602,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -40004,7 +40004,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK197" t="inlineStr">
@@ -40406,7 +40406,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -40808,7 +40808,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -41210,7 +41210,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -41612,7 +41612,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -42014,7 +42014,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -42416,7 +42416,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
@@ -42818,7 +42818,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -43220,7 +43220,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -43622,7 +43622,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -44024,7 +44024,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
@@ -44426,7 +44426,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -44828,7 +44828,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK221" t="inlineStr">
@@ -45230,7 +45230,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -45632,7 +45632,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -46034,7 +46034,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -46436,7 +46436,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -46838,7 +46838,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -47240,7 +47240,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -47642,7 +47642,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -48044,7 +48044,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -48446,7 +48446,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">
@@ -48848,7 +48848,7 @@
       </c>
       <c r="AJ241" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK241" t="inlineStr">

--- a/diseases/d221/2010-2014.xlsx
+++ b/diseases/d221/2010-2014.xlsx
@@ -1010,7 +1010,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3824,7 +3824,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4628,7 +4628,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5030,7 +5030,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5432,7 +5432,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5834,7 +5834,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6638,7 +6638,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7040,7 +7040,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7442,7 +7442,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7844,7 +7844,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8246,7 +8246,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8648,7 +8648,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -9050,7 +9050,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9452,7 +9452,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9854,7 +9854,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10658,7 +10658,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11060,7 +11060,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11462,7 +11462,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11864,7 +11864,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12266,7 +12266,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12668,7 +12668,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -13070,7 +13070,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13472,7 +13472,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14276,7 +14276,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14678,7 +14678,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -15080,7 +15080,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15482,7 +15482,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15884,7 +15884,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16286,7 +16286,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -17090,7 +17090,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17492,7 +17492,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17894,7 +17894,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18296,7 +18296,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18698,7 +18698,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -19100,7 +19100,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19502,7 +19502,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19904,7 +19904,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -20306,7 +20306,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20708,7 +20708,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -21110,7 +21110,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21512,7 +21512,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21914,7 +21914,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -22316,7 +22316,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -22718,7 +22718,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -23120,7 +23120,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23522,7 +23522,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23924,7 +23924,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -24326,7 +24326,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24728,7 +24728,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -25130,7 +25130,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25532,7 +25532,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -25934,7 +25934,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -26336,7 +26336,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -26738,7 +26738,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -27140,7 +27140,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -27542,7 +27542,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -27944,7 +27944,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -28346,7 +28346,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28748,7 +28748,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -29150,7 +29150,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -29552,7 +29552,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -29954,7 +29954,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -30356,7 +30356,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -30758,7 +30758,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -31160,7 +31160,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -31562,7 +31562,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -31964,7 +31964,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -32366,7 +32366,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -32768,7 +32768,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -33170,7 +33170,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -33572,7 +33572,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -33974,7 +33974,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -34376,7 +34376,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -34778,7 +34778,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -35180,7 +35180,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -35582,7 +35582,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -35984,7 +35984,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -36386,7 +36386,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -36788,7 +36788,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -37190,7 +37190,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -37592,7 +37592,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -37994,7 +37994,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -38396,7 +38396,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -38798,7 +38798,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -39200,7 +39200,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK193" t="inlineStr">
@@ -39602,7 +39602,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -40004,7 +40004,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK197" t="inlineStr">
@@ -40406,7 +40406,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -40808,7 +40808,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -41210,7 +41210,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -41612,7 +41612,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -42014,7 +42014,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -42416,7 +42416,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
@@ -42818,7 +42818,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -43220,7 +43220,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -43622,7 +43622,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -44024,7 +44024,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
@@ -44426,7 +44426,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -44828,7 +44828,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK221" t="inlineStr">
@@ -45230,7 +45230,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -45632,7 +45632,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -46034,7 +46034,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -46436,7 +46436,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -46838,7 +46838,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -47240,7 +47240,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -47642,7 +47642,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -48044,7 +48044,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -48446,7 +48446,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">
@@ -48848,7 +48848,7 @@
       </c>
       <c r="AJ241" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK241" t="inlineStr">
